--- a/docs/datos-prueba/insumos-con-errores.xlsx
+++ b/docs/datos-prueba/insumos-con-errores.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:C11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -409,9 +409,6 @@
       <c r="C1" t="str">
         <v>grupo</v>
       </c>
-      <c r="D1" t="str">
-        <v>valorUnitario</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -421,10 +418,7 @@
         <v>kg</v>
       </c>
       <c r="C2" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D2">
-        <v>5900</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="3">
@@ -435,10 +429,7 @@
         <v>kg</v>
       </c>
       <c r="C3" t="str">
-        <v>MATERIALS</v>
-      </c>
-      <c r="D3">
-        <v>18500</v>
+        <v>MATERIALES</v>
       </c>
     </row>
     <row r="4">
@@ -449,10 +440,7 @@
         <v>m2</v>
       </c>
       <c r="C4" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D4" t="str">
-        <v>abc</v>
+        <v>MANO DE OBRA</v>
       </c>
     </row>
     <row r="5">
@@ -463,10 +451,7 @@
         <v>m2</v>
       </c>
       <c r="C5" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D5">
-        <v>12000</v>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="6">
@@ -474,13 +459,10 @@
         <v>Lámina de drywall 1/2</v>
       </c>
       <c r="B6" t="str">
-        <v>und</v>
+        <v/>
       </c>
       <c r="C6" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
+        <v>MATERIAL</v>
       </c>
     </row>
     <row r="7">
@@ -491,10 +473,7 @@
         <v>ml</v>
       </c>
       <c r="C7" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D7">
-        <v>4200</v>
+        <v>material</v>
       </c>
     </row>
     <row r="8">
@@ -507,9 +486,6 @@
       <c r="C8" t="str">
         <v>MANO_OBRA</v>
       </c>
-      <c r="D8">
-        <v>105000</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -519,43 +495,34 @@
         <v>día</v>
       </c>
       <c r="C9" t="str">
-        <v>EQUIPOS</v>
-      </c>
-      <c r="D9">
-        <v>-450000</v>
+        <v>MAQUINARIA</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Retroexcavadora</v>
+        <v>Andamio colgante</v>
       </c>
       <c r="B10" t="str">
         <v>día</v>
       </c>
       <c r="C10" t="str">
-        <v>MAQUINARIA</v>
-      </c>
-      <c r="D10">
-        <v>620000</v>
+        <v>EQUIPO</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Anclaje químico, cartucho 300 ml</v>
+        <v>Andamio colgante</v>
       </c>
       <c r="B11" t="str">
-        <v>und</v>
+        <v>día</v>
       </c>
       <c r="C11" t="str">
-        <v>MATERIALES</v>
-      </c>
-      <c r="D11">
-        <v>72.5</v>
+        <v>EQUIPO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C11"/>
   </ignoredErrors>
 </worksheet>
 </file>